--- a/results/Int Task Remove ACC -0.5/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_4_permute.xlsx
@@ -440,427 +440,427 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6066759353728011</v>
+        <v>0.6594922299696389</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6080812192401424</v>
+        <v>0.6592976928675015</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6109458837957995</v>
+        <v>0.658324831145672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6066001645812078</v>
+        <v>0.6608975138369799</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.623841896313839</v>
+        <v>0.680560562888876</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6334302494621156</v>
+        <v>0.680560562888876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5894784326371232</v>
+        <v>0.680560562888876</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5889487419405428</v>
+        <v>0.69760775751937</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6151516913626585</v>
+        <v>0.6894461859979102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6152706338843456</v>
+        <v>0.6909052142639396</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5974995638774205</v>
+        <v>0.6876516517151512</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.610039101252685</v>
+        <v>0.6805388889182574</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6201139733674479</v>
+        <v>0.678225589029799</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6325335109541657</v>
+        <v>0.6967534858969411</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6320038202575855</v>
+        <v>0.6774365155303691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6237451563962002</v>
+        <v>0.6735774914934071</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6237451563962002</v>
+        <v>0.6863545614897595</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6196695688641958</v>
+        <v>0.6826143037633414</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6254205719461288</v>
+        <v>0.6695663972398287</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6123189210239277</v>
+        <v>0.6704744132609458</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6111081742587239</v>
+        <v>0.6699122997140093</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6126755723778461</v>
+        <v>0.6745820712210199</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5936498790310502</v>
+        <v>0.670765690280722</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5977358630205056</v>
+        <v>0.6649283437386013</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6056368182611132</v>
+        <v>0.6646148641147769</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6059502978849376</v>
+        <v>0.6640960985090776</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6212681563556717</v>
+        <v>0.6837052269511419</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5714560855399373</v>
+        <v>0.6786571301195945</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5767205696553839</v>
+        <v>0.6580427171053442</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5969564811339539</v>
+        <v>0.6299483172716877</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5813794160715136</v>
+        <v>0.6231599591894992</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5585812183590866</v>
+        <v>0.6224466564816626</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5565059797251459</v>
+        <v>0.6510060775223303</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5443662654338934</v>
+        <v>0.6361861917423934</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5443662654338934</v>
+        <v>0.6696203178496603</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5404855674263129</v>
+        <v>0.6667882523555024</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5676287795087586</v>
+        <v>0.6513303060258925</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5660939804511358</v>
+        <v>0.6586591036843987</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5655318669041993</v>
+        <v>0.6598589253587219</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5672289564247464</v>
+        <v>0.6230630430607171</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5640617373361456</v>
+        <v>0.556852939466186</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5451659116019179</v>
+        <v>0.5232017212304472</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5376640746007496</v>
+        <v>0.4520622871149126</v>
       </c>
     </row>
     <row r="45">
@@ -870,393 +870,393 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5348852248718504</v>
+        <v>0.4559429851224931</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5377713871869829</v>
+        <v>0.4559429851224931</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5152110745179304</v>
+        <v>0.4559429851224931</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5409389586978701</v>
+        <v>0.5028986733063026</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5384852185282493</v>
+        <v>0.5046930313779183</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5208434875004625</v>
+        <v>0.5403438936671477</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5218163492222921</v>
+        <v>0.5249825110440334</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5218163492222921</v>
+        <v>0.524885418704108</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5184760907910294</v>
+        <v>0.5251664754775762</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5239888564073014</v>
+        <v>0.5312743061245707</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5626992727766118</v>
+        <v>0.5317391511204386</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5380635452624754</v>
+        <v>0.5832911307645273</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5279779242679749</v>
+        <v>0.6074297666435831</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5336854031975274</v>
+        <v>0.6139263190725655</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5336854031975274</v>
+        <v>0.5832365053101227</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5370256616287901</v>
+        <v>0.5783612716100941</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.535155532765581</v>
+        <v>0.5837661960067031</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5336963282884083</v>
+        <v>0.5763288522839607</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5201619027984092</v>
+        <v>0.5700159118662346</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5359447824761543</v>
+        <v>0.562351784402142</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5067143494020274</v>
+        <v>0.5783073510002625</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5269506133028841</v>
+        <v>0.5780262942267943</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5250697355599373</v>
+        <v>0.5780262942267943</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5250697355599373</v>
+        <v>0.5746860357955317</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5117085256237434</v>
+        <v>0.5722971413266232</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5242697369696265</v>
+        <v>0.5765022440489092</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5281287610065886</v>
+        <v>0.6419879436335795</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5056221927362242</v>
+        <v>0.6703963517244904</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5037629889638962</v>
+        <v>0.6954428274135199</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5037629889638962</v>
+        <v>0.6954104045631637</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4994174459604476</v>
+        <v>0.7077985765663849</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5050059823683131</v>
+        <v>0.7075175197929167</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5084218353800257</v>
+        <v>0.7168896618684373</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5143999746255954</v>
+        <v>0.7055284484080204</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5107786594208644</v>
+        <v>0.5954620344281332</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5048001677530083</v>
+        <v>0.5952134005050211</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4992437017732128</v>
+        <v>0.5303217086842138</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5002810567734682</v>
+        <v>0.5370670712474516</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5002810567734682</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1266,7 +1266,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1276,51 +1276,51 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.501372861016985</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5002162110727558</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5002162110727558</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5001837882223996</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5001837882223996</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
